--- a/test_files/file3.xlsx
+++ b/test_files/file3.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Time</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Coin</t>
   </si>
@@ -25,10 +22,7 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>BNB</t>
+    <t>ADA</t>
   </si>
 </sst>
 </file>
@@ -386,29 +380,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="B2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
